--- a/12603190.xlsx
+++ b/12603190.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amy sarma\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9E4E523E-F133-4721-B6D7-FEF0259C4F5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{47503292-7662-4F68-A2BE-12735EEED6F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -203,6 +203,12 @@
   </si>
   <si>
     <t>MCA/D1P2631</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>I’m feeling exhausted</t>
   </si>
 </sst>
 </file>
@@ -1074,26 +1080,50 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15" t="str">
+      <c r="A8" s="13">
+        <v>46251</v>
+      </c>
+      <c r="B8" s="14">
+        <v>400</v>
+      </c>
+      <c r="C8" s="14">
+        <v>15</v>
+      </c>
+      <c r="D8" s="14">
+        <v>65</v>
+      </c>
+      <c r="E8" s="14">
+        <v>100</v>
+      </c>
+      <c r="F8" s="14">
+        <v>480</v>
+      </c>
+      <c r="G8" s="14">
+        <v>3</v>
+      </c>
+      <c r="H8" s="14">
+        <v>40</v>
+      </c>
+      <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="15" t="str">
+        <v>1100</v>
+      </c>
+      <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="17"/>
+        <v>340</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N8" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="13"/>
